--- a/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260612_212403.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260612_212403.xlsx
@@ -6280,7 +6280,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6490,7 +6490,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6774,7 +6774,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6914,7 +6914,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260612_212403.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260612_212403.xlsx
@@ -6280,7 +6280,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6490,7 +6490,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6774,7 +6774,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6914,7 +6914,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
